--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -1,40 +1,90 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>symbol</t>
+  </si>
+  <si>
+    <t>action</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>stop_loss</t>
+  </si>
+  <si>
+    <t>take_profit</t>
+  </si>
+  <si>
+    <t>position_size</t>
+  </si>
+  <si>
+    <t>entry_date</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>strategy</t>
+  </si>
+  <si>
+    <t>exit_date</t>
+  </si>
+  <si>
+    <t>exit_price</t>
+  </si>
+  <si>
+    <t>exit_reason</t>
+  </si>
+  <si>
+    <t>profit_loss</t>
+  </si>
+  <si>
+    <t>profit_loss_percent</t>
+  </si>
+  <si>
+    <t>timestamp</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -49,94 +99,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -424,233 +415,58 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:O4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>symbol</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>action</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>price</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>stop_loss</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>take_profit</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>position_size</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>entry_date</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>strategy</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>exit_date</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>exit_price</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>exit_reason</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>profit_loss</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>profit_loss_percent</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SOFI</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>18.44</v>
-      </c>
-      <c r="D2" t="n">
-        <v>17.518</v>
-      </c>
-      <c r="E2" t="n">
-        <v>20.284</v>
-      </c>
-      <c r="F2" t="n">
-        <v>542</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>46238</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2026-08-04 11:43:29 EDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>PFE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>25.37</v>
-      </c>
-      <c r="D3" t="n">
-        <v>24.1015</v>
-      </c>
-      <c r="E3" t="n">
-        <v>27.907</v>
-      </c>
-      <c r="F3" t="n">
-        <v>394</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>46238</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2026-08-04 11:43:29 EDT</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>HPE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Buy</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>52.25</v>
-      </c>
-      <c r="D4" t="n">
-        <v>49.6375</v>
-      </c>
-      <c r="E4" t="n">
-        <v>57.475</v>
-      </c>
-      <c r="F4" t="n">
-        <v>191</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>46238</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SEPA</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2026-08-04 11:43:29 EDT</t>
-        </is>
+    <row r="1" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -1,90 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>symbol</t>
-  </si>
-  <si>
-    <t>action</t>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>stop_loss</t>
-  </si>
-  <si>
-    <t>take_profit</t>
-  </si>
-  <si>
-    <t>position_size</t>
-  </si>
-  <si>
-    <t>entry_date</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>strategy</t>
-  </si>
-  <si>
-    <t>exit_date</t>
-  </si>
-  <si>
-    <t>exit_price</t>
-  </si>
-  <si>
-    <t>exit_reason</t>
-  </si>
-  <si>
-    <t>profit_loss</t>
-  </si>
-  <si>
-    <t>profit_loss_percent</t>
-  </si>
-  <si>
-    <t>timestamp</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  </numFmts>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -99,35 +49,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -415,58 +424,656 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>action</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>stop_loss</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>take_profit</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>position_size</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>entry_date</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>strategy</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>exit_date</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>exit_price</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>exit_reason</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>profit_loss</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>profit_loss_percent</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>18.53</v>
+      </c>
+      <c r="D2" t="n">
+        <v>17.6035</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20.383</v>
+      </c>
+      <c r="F2" t="n">
+        <v>26</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:55:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="D3" t="n">
+        <v>24.168</v>
+      </c>
+      <c r="E3" t="n">
+        <v>27.984</v>
+      </c>
+      <c r="F3" t="n">
+        <v>19</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:55:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>PATH</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="D4" t="n">
+        <v>13.0435</v>
+      </c>
+      <c r="E4" t="n">
+        <v>15.103</v>
+      </c>
+      <c r="F4" t="n">
+        <v>36</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:55:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>43.92</v>
+      </c>
+      <c r="D5" t="n">
+        <v>46.8802</v>
+      </c>
+      <c r="E5" t="n">
+        <v>37.9996</v>
+      </c>
+      <c r="F5" t="n">
+        <v>11</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:55:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CDE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>16.46</v>
+      </c>
+      <c r="D6" t="n">
+        <v>15.5606</v>
+      </c>
+      <c r="E6" t="n">
+        <v>18.2588</v>
+      </c>
+      <c r="F6" t="n">
+        <v>30</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:55:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14.4296</v>
+      </c>
+      <c r="E7" t="n">
+        <v>17.953</v>
+      </c>
+      <c r="F7" t="n">
+        <v>32</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:55:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>52.91</v>
+      </c>
+      <c r="D8" t="n">
+        <v>50.2421</v>
+      </c>
+      <c r="E8" t="n">
+        <v>58.2457</v>
+      </c>
+      <c r="F8" t="n">
+        <v>9</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:55:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>43.68</v>
+      </c>
+      <c r="E9" t="n">
+        <v>37.44</v>
+      </c>
+      <c r="F9" t="n">
+        <v>12</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:55:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>HBAN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>16.815</v>
+      </c>
+      <c r="E10" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="F10" t="n">
+        <v>28</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:55:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>KVUE</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>18.43</v>
+      </c>
+      <c r="E11" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="F11" t="n">
+        <v>25</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:55:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>115.84</v>
+      </c>
+      <c r="D12" t="n">
+        <v>110.048</v>
+      </c>
+      <c r="E12" t="n">
+        <v>127.424</v>
+      </c>
+      <c r="F12" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="G12" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:55:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BSX</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>48.83</v>
+      </c>
+      <c r="D13" t="n">
+        <v>46.3885</v>
+      </c>
+      <c r="E13" t="n">
+        <v>53.713</v>
+      </c>
+      <c r="F13" t="n">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
+      <c r="G13" s="2" t="n">
+        <v>46238</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>2026-08-04 13:55:41 EDT</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1073,6 +1073,570 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>67.73999999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>71.7367</v>
+      </c>
+      <c r="E14" t="n">
+        <v>59.7467</v>
+      </c>
+      <c r="F14" t="n">
+        <v>7</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:13:25 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>100.33</v>
+      </c>
+      <c r="D15" t="n">
+        <v>95.3135</v>
+      </c>
+      <c r="E15" t="n">
+        <v>110.363</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:13:25 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>51.43</v>
+      </c>
+      <c r="D16" t="n">
+        <v>45.7115</v>
+      </c>
+      <c r="E16" t="n">
+        <v>59.1345</v>
+      </c>
+      <c r="F16" t="n">
+        <v>9</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:13:25 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>WBS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>79.18000000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>75.221</v>
+      </c>
+      <c r="E17" t="n">
+        <v>87.098</v>
+      </c>
+      <c r="F17" t="n">
+        <v>6</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:13:25 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ERIC</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="D18" t="n">
+        <v>10.6575</v>
+      </c>
+      <c r="E18" t="n">
+        <v>9.135</v>
+      </c>
+      <c r="F18" t="n">
+        <v>49</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:13:25 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>41.07</v>
+      </c>
+      <c r="D19" t="n">
+        <v>38.2118</v>
+      </c>
+      <c r="E19" t="n">
+        <v>46.7865</v>
+      </c>
+      <c r="F19" t="n">
+        <v>12</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:13:25 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>17.82</v>
+      </c>
+      <c r="D20" t="n">
+        <v>16.4939</v>
+      </c>
+      <c r="E20" t="n">
+        <v>20.4722</v>
+      </c>
+      <c r="F20" t="n">
+        <v>28</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:13:25 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>KGC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>25.73</v>
+      </c>
+      <c r="D21" t="n">
+        <v>23.599</v>
+      </c>
+      <c r="E21" t="n">
+        <v>29.5795</v>
+      </c>
+      <c r="F21" t="n">
+        <v>19</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:13:25 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>77.72</v>
+      </c>
+      <c r="D22" t="n">
+        <v>81.60599999999999</v>
+      </c>
+      <c r="E22" t="n">
+        <v>69.94799999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>6</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:13:25 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GILD</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>130.31</v>
+      </c>
+      <c r="D23" t="n">
+        <v>136.8255</v>
+      </c>
+      <c r="E23" t="n">
+        <v>117.279</v>
+      </c>
+      <c r="F23" t="n">
+        <v>3</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:13:25 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>UMC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="D24" t="n">
+        <v>20.5617</v>
+      </c>
+      <c r="E24" t="n">
+        <v>17.1966</v>
+      </c>
+      <c r="F24" t="n">
+        <v>25</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:13:25 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>DVN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>42.82</v>
+      </c>
+      <c r="D25" t="n">
+        <v>44.961</v>
+      </c>
+      <c r="E25" t="n">
+        <v>38.538</v>
+      </c>
+      <c r="F25" t="n">
+        <v>11</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46239</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>2026-08-05 11:13:25 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1637,6 +1637,570 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>TTD</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>17.92</v>
+      </c>
+      <c r="D26" t="n">
+        <v>18.9074</v>
+      </c>
+      <c r="E26" t="n">
+        <v>15.9452</v>
+      </c>
+      <c r="F26" t="n">
+        <v>27</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:08 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>73.73</v>
+      </c>
+      <c r="D27" t="n">
+        <v>77.4165</v>
+      </c>
+      <c r="E27" t="n">
+        <v>66.357</v>
+      </c>
+      <c r="F27" t="n">
+        <v>6</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:08 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>56.44</v>
+      </c>
+      <c r="D28" t="n">
+        <v>53.618</v>
+      </c>
+      <c r="E28" t="n">
+        <v>62.084</v>
+      </c>
+      <c r="F28" t="n">
+        <v>8</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:08 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>HST</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="D29" t="n">
+        <v>25.0407</v>
+      </c>
+      <c r="E29" t="n">
+        <v>20.8086</v>
+      </c>
+      <c r="F29" t="n">
+        <v>21</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:08 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>VALE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>14.86</v>
+      </c>
+      <c r="D30" t="n">
+        <v>15.603</v>
+      </c>
+      <c r="E30" t="n">
+        <v>13.374</v>
+      </c>
+      <c r="F30" t="n">
+        <v>33</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:08 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AXIA</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10.66</v>
+      </c>
+      <c r="D31" t="n">
+        <v>10.127</v>
+      </c>
+      <c r="E31" t="n">
+        <v>11.726</v>
+      </c>
+      <c r="F31" t="n">
+        <v>46</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:08 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>PBR</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>18.59</v>
+      </c>
+      <c r="D32" t="n">
+        <v>17.6605</v>
+      </c>
+      <c r="E32" t="n">
+        <v>20.449</v>
+      </c>
+      <c r="F32" t="n">
+        <v>26</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:08 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SHEL</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>89.33</v>
+      </c>
+      <c r="D33" t="n">
+        <v>84.8635</v>
+      </c>
+      <c r="E33" t="n">
+        <v>98.26300000000001</v>
+      </c>
+      <c r="F33" t="n">
+        <v>5</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:08 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Z</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>31.81</v>
+      </c>
+      <c r="D34" t="n">
+        <v>35.589</v>
+      </c>
+      <c r="E34" t="n">
+        <v>24.2519</v>
+      </c>
+      <c r="F34" t="n">
+        <v>15</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:08 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>HUBS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>195.7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>238.343</v>
+      </c>
+      <c r="E35" t="n">
+        <v>110.4139</v>
+      </c>
+      <c r="F35" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:08 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>CX</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="D36" t="n">
+        <v>12.0645</v>
+      </c>
+      <c r="E36" t="n">
+        <v>10.341</v>
+      </c>
+      <c r="F36" t="n">
+        <v>43</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:08 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SLB</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="D37" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="E37" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="F37" t="n">
+        <v>9</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46240</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>2026-08-06 11:14:08 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2201,6 +2201,570 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TTD</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="D38" t="n">
+        <v>16.9317</v>
+      </c>
+      <c r="E38" t="n">
+        <v>8.2867</v>
+      </c>
+      <c r="F38" t="n">
+        <v>35</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:13:45 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>DOCS</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>32.73</v>
+      </c>
+      <c r="D39" t="n">
+        <v>20.6603</v>
+      </c>
+      <c r="E39" t="n">
+        <v>37.6295</v>
+      </c>
+      <c r="F39" t="n">
+        <v>15</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:13:45 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>DV</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>11.7139</v>
+      </c>
+      <c r="E40" t="n">
+        <v>15.285</v>
+      </c>
+      <c r="F40" t="n">
+        <v>37</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:13:45 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>74.31</v>
+      </c>
+      <c r="D41" t="n">
+        <v>70.46939999999999</v>
+      </c>
+      <c r="E41" t="n">
+        <v>81.99120000000001</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:13:45 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>17.09</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.2355</v>
+      </c>
+      <c r="E42" t="n">
+        <v>18.799</v>
+      </c>
+      <c r="F42" t="n">
+        <v>29</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:13:45 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ABNB</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>175.71</v>
+      </c>
+      <c r="D43" t="n">
+        <v>151.6441</v>
+      </c>
+      <c r="E43" t="n">
+        <v>202.0565</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:13:45 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>CART</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="D44" t="n">
+        <v>45.0314</v>
+      </c>
+      <c r="E44" t="n">
+        <v>57.628</v>
+      </c>
+      <c r="F44" t="n">
+        <v>9</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:13:45 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>IAG</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>17.52</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.0293</v>
+      </c>
+      <c r="E45" t="n">
+        <v>20.138</v>
+      </c>
+      <c r="F45" t="n">
+        <v>28</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:13:45 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>47.12</v>
+      </c>
+      <c r="D46" t="n">
+        <v>44.764</v>
+      </c>
+      <c r="E46" t="n">
+        <v>51.832</v>
+      </c>
+      <c r="F46" t="n">
+        <v>10</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:13:45 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>NEM</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>112.45</v>
+      </c>
+      <c r="D47" t="n">
+        <v>105.4285</v>
+      </c>
+      <c r="E47" t="n">
+        <v>126.4931</v>
+      </c>
+      <c r="F47" t="n">
+        <v>4</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:13:45 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>CTSH</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="D48" t="n">
+        <v>54.454</v>
+      </c>
+      <c r="E48" t="n">
+        <v>63.052</v>
+      </c>
+      <c r="F48" t="n">
+        <v>8</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:13:45 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FIVN</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="D49" t="n">
+        <v>28.3705</v>
+      </c>
+      <c r="E49" t="n">
+        <v>37.572</v>
+      </c>
+      <c r="F49" t="n">
+        <v>15</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>46241</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>2026-08-07 10:13:45 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O49"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2765,6 +2765,570 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>LFST</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="D50" t="n">
+        <v>10.8356</v>
+      </c>
+      <c r="E50" t="n">
+        <v>13.859</v>
+      </c>
+      <c r="F50" t="n">
+        <v>41</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:20:47 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>CELH</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>26.27</v>
+      </c>
+      <c r="D51" t="n">
+        <v>27.6886</v>
+      </c>
+      <c r="E51" t="n">
+        <v>23.4328</v>
+      </c>
+      <c r="F51" t="n">
+        <v>19</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:20:47 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="D52" t="n">
+        <v>19.475</v>
+      </c>
+      <c r="E52" t="n">
+        <v>22.55</v>
+      </c>
+      <c r="F52" t="n">
+        <v>24</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:20:47 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>CRCL</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>65.20999999999999</v>
+      </c>
+      <c r="D53" t="n">
+        <v>68.4705</v>
+      </c>
+      <c r="E53" t="n">
+        <v>58.689</v>
+      </c>
+      <c r="F53" t="n">
+        <v>7</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:20:47 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>XOM</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>157.76</v>
+      </c>
+      <c r="D54" t="n">
+        <v>149.872</v>
+      </c>
+      <c r="E54" t="n">
+        <v>173.536</v>
+      </c>
+      <c r="F54" t="n">
+        <v>3</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:20:47 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>QCOM</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>166.17</v>
+      </c>
+      <c r="D55" t="n">
+        <v>174.4785</v>
+      </c>
+      <c r="E55" t="n">
+        <v>149.553</v>
+      </c>
+      <c r="F55" t="n">
+        <v>3</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:20:47 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>PINS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>23.95</v>
+      </c>
+      <c r="D56" t="n">
+        <v>22.7525</v>
+      </c>
+      <c r="E56" t="n">
+        <v>26.345</v>
+      </c>
+      <c r="F56" t="n">
+        <v>20</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:20:47 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>NESR</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>34</v>
+      </c>
+      <c r="D57" t="n">
+        <v>29.0152</v>
+      </c>
+      <c r="E57" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="F57" t="n">
+        <v>14</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:20:47 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>KVYO</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>16.89</v>
+      </c>
+      <c r="D58" t="n">
+        <v>16.0455</v>
+      </c>
+      <c r="E58" t="n">
+        <v>18.579</v>
+      </c>
+      <c r="F58" t="n">
+        <v>29</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:20:47 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EQT</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>52.78</v>
+      </c>
+      <c r="D59" t="n">
+        <v>50.141</v>
+      </c>
+      <c r="E59" t="n">
+        <v>58.058</v>
+      </c>
+      <c r="F59" t="n">
+        <v>9</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:20:47 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>VICI</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>26.12</v>
+      </c>
+      <c r="D60" t="n">
+        <v>27.426</v>
+      </c>
+      <c r="E60" t="n">
+        <v>23.508</v>
+      </c>
+      <c r="F60" t="n">
+        <v>19</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:20:47 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>AZN</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>160.57</v>
+      </c>
+      <c r="D61" t="n">
+        <v>168.5985</v>
+      </c>
+      <c r="E61" t="n">
+        <v>144.513</v>
+      </c>
+      <c r="F61" t="n">
+        <v>3</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>46244</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:20:47 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3329,6 +3329,335 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="D62" t="n">
+        <v>37.3754</v>
+      </c>
+      <c r="E62" t="n">
+        <v>19.4492</v>
+      </c>
+      <c r="F62" t="n">
+        <v>15</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:20:27 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>PATH</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>15.76</v>
+      </c>
+      <c r="D63" t="n">
+        <v>14.972</v>
+      </c>
+      <c r="E63" t="n">
+        <v>17.336</v>
+      </c>
+      <c r="F63" t="n">
+        <v>31</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:20:27 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>CRCL</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>72.88</v>
+      </c>
+      <c r="D64" t="n">
+        <v>67.0531</v>
+      </c>
+      <c r="E64" t="n">
+        <v>83.80200000000001</v>
+      </c>
+      <c r="F64" t="n">
+        <v>6</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:20:27 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>CDE</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>18.3</v>
+      </c>
+      <c r="D65" t="n">
+        <v>17.385</v>
+      </c>
+      <c r="E65" t="n">
+        <v>20.13</v>
+      </c>
+      <c r="F65" t="n">
+        <v>27</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:20:27 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>144.32</v>
+      </c>
+      <c r="D66" t="n">
+        <v>151.536</v>
+      </c>
+      <c r="E66" t="n">
+        <v>129.888</v>
+      </c>
+      <c r="F66" t="n">
+        <v>3</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:20:27 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="D67" t="n">
+        <v>20.273</v>
+      </c>
+      <c r="E67" t="n">
+        <v>23.474</v>
+      </c>
+      <c r="F67" t="n">
+        <v>23</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:20:27 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>ALC</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>75.45</v>
+      </c>
+      <c r="D68" t="n">
+        <v>71.67749999999999</v>
+      </c>
+      <c r="E68" t="n">
+        <v>82.995</v>
+      </c>
+      <c r="F68" t="n">
+        <v>6</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>46245</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2026-08-11 10:20:27 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O68"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3658,6 +3658,288 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>18.16</v>
+      </c>
+      <c r="D69" t="n">
+        <v>17.252</v>
+      </c>
+      <c r="E69" t="n">
+        <v>19.976</v>
+      </c>
+      <c r="F69" t="n">
+        <v>27</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:21:42 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>GME</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="D70" t="n">
+        <v>19.488</v>
+      </c>
+      <c r="E70" t="n">
+        <v>16.704</v>
+      </c>
+      <c r="F70" t="n">
+        <v>26</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:21:42 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>CPRT</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>28.92</v>
+      </c>
+      <c r="D71" t="n">
+        <v>30.366</v>
+      </c>
+      <c r="E71" t="n">
+        <v>26.028</v>
+      </c>
+      <c r="F71" t="n">
+        <v>17</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:21:42 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>GFI</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>41.5</v>
+      </c>
+      <c r="D72" t="n">
+        <v>39.425</v>
+      </c>
+      <c r="E72" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="F72" t="n">
+        <v>12</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:21:42 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>PAAS</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>52.82</v>
+      </c>
+      <c r="D73" t="n">
+        <v>50.179</v>
+      </c>
+      <c r="E73" t="n">
+        <v>58.102</v>
+      </c>
+      <c r="F73" t="n">
+        <v>9</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:21:42 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>GMAB</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="D74" t="n">
+        <v>29.7825</v>
+      </c>
+      <c r="E74" t="n">
+        <v>34.485</v>
+      </c>
+      <c r="F74" t="n">
+        <v>15</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>46246</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2026-08-12 10:21:42 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3940,6 +3940,288 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>CLBT</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="D75" t="n">
+        <v>13.7072</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3.7856</v>
+      </c>
+      <c r="F75" t="n">
+        <v>48</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:23:35 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>NFLX</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>77.56</v>
+      </c>
+      <c r="D76" t="n">
+        <v>73.682</v>
+      </c>
+      <c r="E76" t="n">
+        <v>85.316</v>
+      </c>
+      <c r="F76" t="n">
+        <v>6</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:23:35 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>61.81</v>
+      </c>
+      <c r="D77" t="n">
+        <v>58.7195</v>
+      </c>
+      <c r="E77" t="n">
+        <v>67.991</v>
+      </c>
+      <c r="F77" t="n">
+        <v>8</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:23:35 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>PYPL</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>59.92</v>
+      </c>
+      <c r="D78" t="n">
+        <v>56.924</v>
+      </c>
+      <c r="E78" t="n">
+        <v>65.91200000000001</v>
+      </c>
+      <c r="F78" t="n">
+        <v>8</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:23:35 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>YETI</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>44.79</v>
+      </c>
+      <c r="D79" t="n">
+        <v>50.12</v>
+      </c>
+      <c r="E79" t="n">
+        <v>34.13</v>
+      </c>
+      <c r="F79" t="n">
+        <v>11</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:23:35 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BIRK</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>43.56</v>
+      </c>
+      <c r="D80" t="n">
+        <v>36.7409</v>
+      </c>
+      <c r="E80" t="n">
+        <v>50.084</v>
+      </c>
+      <c r="F80" t="n">
+        <v>11</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46247</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2026-08-13 10:23:35 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4222,6 +4222,194 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>CPRT</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>30.84</v>
+      </c>
+      <c r="D81" t="n">
+        <v>29.298</v>
+      </c>
+      <c r="E81" t="n">
+        <v>33.924</v>
+      </c>
+      <c r="F81" t="n">
+        <v>16</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:16:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>CVX</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>200.37</v>
+      </c>
+      <c r="D82" t="n">
+        <v>190.3515</v>
+      </c>
+      <c r="E82" t="n">
+        <v>220.407</v>
+      </c>
+      <c r="F82" t="n">
+        <v>2</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:16:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>OSCR</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>32.31</v>
+      </c>
+      <c r="D83" t="n">
+        <v>30.6945</v>
+      </c>
+      <c r="E83" t="n">
+        <v>35.541</v>
+      </c>
+      <c r="F83" t="n">
+        <v>15</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:16:41 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>FOXA</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>68.65000000000001</v>
+      </c>
+      <c r="D84" t="n">
+        <v>65.2175</v>
+      </c>
+      <c r="E84" t="n">
+        <v>75.515</v>
+      </c>
+      <c r="F84" t="n">
+        <v>7</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46248</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>2026-08-14 10:16:42 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O84"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4410,6 +4410,53 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SKHY</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>172.93</v>
+      </c>
+      <c r="D85" t="n">
+        <v>164.2835</v>
+      </c>
+      <c r="E85" t="n">
+        <v>190.223</v>
+      </c>
+      <c r="F85" t="n">
+        <v>2</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46251</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2026-08-17 10:06:39 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4457,6 +4457,335 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>PFE</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>27.2</v>
+      </c>
+      <c r="D86" t="n">
+        <v>25.84</v>
+      </c>
+      <c r="E86" t="n">
+        <v>29.92</v>
+      </c>
+      <c r="F86" t="n">
+        <v>18</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:18:38 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>NOW</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>120.36</v>
+      </c>
+      <c r="D87" t="n">
+        <v>114.342</v>
+      </c>
+      <c r="E87" t="n">
+        <v>132.396</v>
+      </c>
+      <c r="F87" t="n">
+        <v>4</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:18:38 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>PBR-A</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>16.52</v>
+      </c>
+      <c r="D88" t="n">
+        <v>15.694</v>
+      </c>
+      <c r="E88" t="n">
+        <v>18.172</v>
+      </c>
+      <c r="F88" t="n">
+        <v>30</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:18:38 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="D89" t="n">
+        <v>11.1815</v>
+      </c>
+      <c r="E89" t="n">
+        <v>12.947</v>
+      </c>
+      <c r="F89" t="n">
+        <v>42</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:18:38 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>HAL</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>34.96</v>
+      </c>
+      <c r="D90" t="n">
+        <v>33.212</v>
+      </c>
+      <c r="E90" t="n">
+        <v>38.456</v>
+      </c>
+      <c r="F90" t="n">
+        <v>14</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:18:38 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>ON</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>78.70999999999999</v>
+      </c>
+      <c r="D91" t="n">
+        <v>83.1178</v>
+      </c>
+      <c r="E91" t="n">
+        <v>69.89449999999999</v>
+      </c>
+      <c r="F91" t="n">
+        <v>6</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:18:38 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>JNJ</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>269.77</v>
+      </c>
+      <c r="D92" t="n">
+        <v>256.2815</v>
+      </c>
+      <c r="E92" t="n">
+        <v>296.747</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46252</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>2026-08-18 10:18:38 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4786,6 +4786,429 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SKHY</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>156.94</v>
+      </c>
+      <c r="D93" t="n">
+        <v>149.093</v>
+      </c>
+      <c r="E93" t="n">
+        <v>172.634</v>
+      </c>
+      <c r="F93" t="n">
+        <v>3</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:19:55 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>CDE</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>20.33</v>
+      </c>
+      <c r="D94" t="n">
+        <v>18.5138</v>
+      </c>
+      <c r="E94" t="n">
+        <v>23.3695</v>
+      </c>
+      <c r="F94" t="n">
+        <v>24</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:19:55 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>45.06</v>
+      </c>
+      <c r="D95" t="n">
+        <v>42.0885</v>
+      </c>
+      <c r="E95" t="n">
+        <v>51.0029</v>
+      </c>
+      <c r="F95" t="n">
+        <v>11</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:19:55 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>AG</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>18.4794</v>
+      </c>
+      <c r="E96" t="n">
+        <v>23.105</v>
+      </c>
+      <c r="F96" t="n">
+        <v>24</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:19:55 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>KGC</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="D97" t="n">
+        <v>27.1256</v>
+      </c>
+      <c r="E97" t="n">
+        <v>34.1105</v>
+      </c>
+      <c r="F97" t="n">
+        <v>16</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:19:55 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>BSX</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>52.37</v>
+      </c>
+      <c r="D98" t="n">
+        <v>49.7515</v>
+      </c>
+      <c r="E98" t="n">
+        <v>57.607</v>
+      </c>
+      <c r="F98" t="n">
+        <v>9</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:19:55 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>UMC</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>18</v>
+      </c>
+      <c r="D99" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="E99" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F99" t="n">
+        <v>27</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:19:55 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>KVUE</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>19.05</v>
+      </c>
+      <c r="D100" t="n">
+        <v>18.0975</v>
+      </c>
+      <c r="E100" t="n">
+        <v>20.955</v>
+      </c>
+      <c r="F100" t="n">
+        <v>26</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:19:55 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>FSM</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>11.49</v>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4502</v>
+      </c>
+      <c r="E101" t="n">
+        <v>13.2035</v>
+      </c>
+      <c r="F101" t="n">
+        <v>43</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>46253</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>2026-08-19 10:19:55 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:O111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5209,6 +5209,476 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>39.93</v>
+      </c>
+      <c r="D102" t="n">
+        <v>41.9265</v>
+      </c>
+      <c r="E102" t="n">
+        <v>35.937</v>
+      </c>
+      <c r="F102" t="n">
+        <v>12</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:36:49 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PBR</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>18.145</v>
+      </c>
+      <c r="E103" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="F103" t="n">
+        <v>26</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:36:49 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>HL</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="D104" t="n">
+        <v>19.646</v>
+      </c>
+      <c r="E104" t="n">
+        <v>22.748</v>
+      </c>
+      <c r="F104" t="n">
+        <v>24</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:36:49 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>23.85</v>
+      </c>
+      <c r="D105" t="n">
+        <v>22.6575</v>
+      </c>
+      <c r="E105" t="n">
+        <v>26.235</v>
+      </c>
+      <c r="F105" t="n">
+        <v>20</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:36:49 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>OXY</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>61.69</v>
+      </c>
+      <c r="D106" t="n">
+        <v>58.6055</v>
+      </c>
+      <c r="E106" t="n">
+        <v>67.85899999999999</v>
+      </c>
+      <c r="F106" t="n">
+        <v>8</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" t="inlineStr"/>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:36:49 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>HPE</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="D107" t="n">
+        <v>50.901</v>
+      </c>
+      <c r="E107" t="n">
+        <v>58.938</v>
+      </c>
+      <c r="F107" t="n">
+        <v>9</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" t="inlineStr"/>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:36:49 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>RDDT</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>146.06</v>
+      </c>
+      <c r="D108" t="n">
+        <v>153.363</v>
+      </c>
+      <c r="E108" t="n">
+        <v>131.454</v>
+      </c>
+      <c r="F108" t="n">
+        <v>3</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr"/>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:36:49 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>134.8</v>
+      </c>
+      <c r="D109" t="n">
+        <v>128.06</v>
+      </c>
+      <c r="E109" t="n">
+        <v>148.28</v>
+      </c>
+      <c r="F109" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:36:49 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>APA</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="D110" t="n">
+        <v>42.4175</v>
+      </c>
+      <c r="E110" t="n">
+        <v>49.115</v>
+      </c>
+      <c r="F110" t="n">
+        <v>11</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:36:49 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>37.16</v>
+      </c>
+      <c r="D111" t="n">
+        <v>35.302</v>
+      </c>
+      <c r="E111" t="n">
+        <v>40.876</v>
+      </c>
+      <c r="F111" t="n">
+        <v>13</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>46254</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>2026-08-20 10:36:49 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O111"/>
+  <dimension ref="A1:O123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5679,6 +5679,570 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>CRCL</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>89.38</v>
+      </c>
+      <c r="D112" t="n">
+        <v>83.6656</v>
+      </c>
+      <c r="E112" t="n">
+        <v>100.8087</v>
+      </c>
+      <c r="F112" t="n">
+        <v>5</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:21:12 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>VALE</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="D113" t="n">
+        <v>13.889</v>
+      </c>
+      <c r="E113" t="n">
+        <v>16.082</v>
+      </c>
+      <c r="F113" t="n">
+        <v>34</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:21:12 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>BSX</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>49.85</v>
+      </c>
+      <c r="D114" t="n">
+        <v>47.3575</v>
+      </c>
+      <c r="E114" t="n">
+        <v>54.835</v>
+      </c>
+      <c r="F114" t="n">
+        <v>10</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:21:12 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>TTD</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>13.24</v>
+      </c>
+      <c r="D115" t="n">
+        <v>13.902</v>
+      </c>
+      <c r="E115" t="n">
+        <v>11.916</v>
+      </c>
+      <c r="F115" t="n">
+        <v>37</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:21:12 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>ROST</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>235.46</v>
+      </c>
+      <c r="D116" t="n">
+        <v>223.687</v>
+      </c>
+      <c r="E116" t="n">
+        <v>259.006</v>
+      </c>
+      <c r="F116" t="n">
+        <v>2</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:21:12 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>NEM</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>131.21</v>
+      </c>
+      <c r="D117" t="n">
+        <v>124.6495</v>
+      </c>
+      <c r="E117" t="n">
+        <v>144.331</v>
+      </c>
+      <c r="F117" t="n">
+        <v>3</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:21:12 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>XYZ</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>81.26000000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>77.197</v>
+      </c>
+      <c r="E118" t="n">
+        <v>89.386</v>
+      </c>
+      <c r="F118" t="n">
+        <v>6</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:21:12 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>GFI</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>48.21</v>
+      </c>
+      <c r="D119" t="n">
+        <v>45.4554</v>
+      </c>
+      <c r="E119" t="n">
+        <v>53.7192</v>
+      </c>
+      <c r="F119" t="n">
+        <v>10</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:21:13 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>HMY</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="D120" t="n">
+        <v>22.0202</v>
+      </c>
+      <c r="E120" t="n">
+        <v>26.4595</v>
+      </c>
+      <c r="F120" t="n">
+        <v>21</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:21:13 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>IAG</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="D121" t="n">
+        <v>19.9215</v>
+      </c>
+      <c r="E121" t="n">
+        <v>23.067</v>
+      </c>
+      <c r="F121" t="n">
+        <v>23</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:21:13 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>AEM</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>216.93</v>
+      </c>
+      <c r="D122" t="n">
+        <v>206.0835</v>
+      </c>
+      <c r="E122" t="n">
+        <v>238.623</v>
+      </c>
+      <c r="F122" t="n">
+        <v>2</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:21:13 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>TECK</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>68.59</v>
+      </c>
+      <c r="D123" t="n">
+        <v>65.1605</v>
+      </c>
+      <c r="E123" t="n">
+        <v>75.449</v>
+      </c>
+      <c r="F123" t="n">
+        <v>7</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>2026-08-21 10:21:13 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O123"/>
+  <dimension ref="A1:O127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6243,6 +6243,194 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>HLN</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="D124" t="n">
+        <v>9.670999999999999</v>
+      </c>
+      <c r="E124" t="n">
+        <v>11.198</v>
+      </c>
+      <c r="F124" t="n">
+        <v>49</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:52:24 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ACN</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>186.64</v>
+      </c>
+      <c r="D125" t="n">
+        <v>177.308</v>
+      </c>
+      <c r="E125" t="n">
+        <v>205.304</v>
+      </c>
+      <c r="F125" t="n">
+        <v>2</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:52:24 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>DIS</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>110.29</v>
+      </c>
+      <c r="D126" t="n">
+        <v>104.7755</v>
+      </c>
+      <c r="E126" t="n">
+        <v>121.319</v>
+      </c>
+      <c r="F126" t="n">
+        <v>4</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:52:24 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>JD</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="D127" t="n">
+        <v>30.5235</v>
+      </c>
+      <c r="E127" t="n">
+        <v>26.163</v>
+      </c>
+      <c r="F127" t="n">
+        <v>17</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>46258</v>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>2026-08-24 09:52:24 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O127"/>
+  <dimension ref="A1:O136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6431,6 +6431,429 @@
         </is>
       </c>
     </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>NVO</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>47.71</v>
+      </c>
+      <c r="D128" t="n">
+        <v>45.3245</v>
+      </c>
+      <c r="E128" t="n">
+        <v>52.481</v>
+      </c>
+      <c r="F128" t="n">
+        <v>10</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:51:17 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>PBR</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>17.93</v>
+      </c>
+      <c r="D129" t="n">
+        <v>18.8265</v>
+      </c>
+      <c r="E129" t="n">
+        <v>16.137</v>
+      </c>
+      <c r="F129" t="n">
+        <v>27</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:51:17 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ONON</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>28.79</v>
+      </c>
+      <c r="D130" t="n">
+        <v>30.2295</v>
+      </c>
+      <c r="E130" t="n">
+        <v>25.911</v>
+      </c>
+      <c r="F130" t="n">
+        <v>17</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:51:17 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>PG</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>145.21</v>
+      </c>
+      <c r="D131" t="n">
+        <v>152.4705</v>
+      </c>
+      <c r="E131" t="n">
+        <v>130.689</v>
+      </c>
+      <c r="F131" t="n">
+        <v>3</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:51:17 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>VICI</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>26.55</v>
+      </c>
+      <c r="D132" t="n">
+        <v>27.8775</v>
+      </c>
+      <c r="E132" t="n">
+        <v>23.895</v>
+      </c>
+      <c r="F132" t="n">
+        <v>18</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:51:17 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>UBER</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>79.78</v>
+      </c>
+      <c r="D133" t="n">
+        <v>75.791</v>
+      </c>
+      <c r="E133" t="n">
+        <v>87.758</v>
+      </c>
+      <c r="F133" t="n">
+        <v>6</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:51:17 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>DT</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="D134" t="n">
+        <v>47.8515</v>
+      </c>
+      <c r="E134" t="n">
+        <v>55.407</v>
+      </c>
+      <c r="F134" t="n">
+        <v>9</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:51:17 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>AMRZ</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>43.85</v>
+      </c>
+      <c r="D135" t="n">
+        <v>46.0425</v>
+      </c>
+      <c r="E135" t="n">
+        <v>39.465</v>
+      </c>
+      <c r="F135" t="n">
+        <v>11</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:51:17 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>LYFT</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>17.85</v>
+      </c>
+      <c r="D136" t="n">
+        <v>16.9575</v>
+      </c>
+      <c r="E136" t="n">
+        <v>19.635</v>
+      </c>
+      <c r="F136" t="n">
+        <v>28</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>46259</v>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>2026-08-25 09:51:17 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/signals_log.xlsx
+++ b/data/signals_log.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O136"/>
+  <dimension ref="A1:O140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6854,6 +6854,194 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>PLAB</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>30.91</v>
+      </c>
+      <c r="D137" t="n">
+        <v>29.3208</v>
+      </c>
+      <c r="E137" t="n">
+        <v>34.0884</v>
+      </c>
+      <c r="F137" t="n">
+        <v>16</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:55:24 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ANF</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>140.45</v>
+      </c>
+      <c r="D138" t="n">
+        <v>108.9013</v>
+      </c>
+      <c r="E138" t="n">
+        <v>161.5075</v>
+      </c>
+      <c r="F138" t="n">
+        <v>3</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:55:24 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ZM</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>94.76000000000001</v>
+      </c>
+      <c r="D139" t="n">
+        <v>100.5498</v>
+      </c>
+      <c r="E139" t="n">
+        <v>83.1803</v>
+      </c>
+      <c r="F139" t="n">
+        <v>5</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:55:24 EDT</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ERIC</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="D140" t="n">
+        <v>10.6785</v>
+      </c>
+      <c r="E140" t="n">
+        <v>9.153</v>
+      </c>
+      <c r="F140" t="n">
+        <v>49</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>46260</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>SEPA</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>2026-08-26 09:55:24 EDT</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
